--- a/stories/arbres/ATOM-TMP.JOU.001-07.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le jour, Gaëtane joue au jardin avec maman. Le soleil brille. Il fait chaud sur les mains. Maman dit : le jour, c'est le soleil. Gaëtane touche une pierre tiède. Parce que le soleil a chauffé. Elles rangent le seau. Le soir arrive. Le ciel devient bleu foncé. Gaëtane voit la lune. Elle voit les étoiles. Maman dit : la nuit, c'est la lune. Elles rentrent. Gaëtane met son pyjama. Maman dit : la nuit, on fait dodo. Gaëtane se couche. Elle ferme les yeux. Dodo la nuit. Soleil jour. Lune nuit. Plus tard, Gaëtane se réveille un peu. Elle se souvient. Le jour, le soleil. La nuit, la lune. Dodo la nuit.</t>
+          <t>Le jour, Gaëtane joue au jardin avec maman. Le soleil brille. Il fait chaud sur les mains. Le jour, c'est le soleil. Gaëtane touche une pierre tiède. Parce que le soleil a chauffé. Elles rangent le seau. Le soir arrive. Le ciel devient bleu foncé. Gaëtane voit la lune. Elle voit les étoiles. La nuit, c'est la lune. Elles rentrent. Gaëtane met son pyjama. La nuit, on fait dodo. Gaëtane se couche. Elle ferme les yeux. Dodo la nuit. Soleil jour. Lune nuit. Plus tard, Gaëtane se réveille un peu. Elle se souvient. Le jour, le soleil. La nuit, la lune. Dodo la nuit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le jour, Gaëtane joue au jardin avec maman. Le soleil brille. Il fait chaud sur les mains.
+maman|Le jour, c'est le soleil.
+narrateur|Gaëtane touche une pierre tiède. Parce que le soleil a chauffé. Elles rangent le seau. Le soir arrive. Le ciel devient bleu foncé. Gaëtane voit la lune. Elle voit les étoiles.
+maman|La nuit, c'est la lune. Elles rentrent.
+narrateur|Gaëtane met son pyjama.
+maman|La nuit, on fait dodo.
+narrateur|Gaëtane se couche. Elle ferme les yeux. Dodo la nuit. Soleil jour. Lune nuit. Plus tard, Gaëtane se réveille un peu. Elle se souvient. Le jour, le soleil. La nuit, la lune. Dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La lune est là. Quel moment est-ce ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Gaëtane a vu le soleil le jour. Elle a vu la lune la nuit. Elle fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1836,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman baisse la lumière. Gaëtane respire.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2003,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2043,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.JOU.001-07.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Gaëtane se couche. Elle ferme les yeux. Dodo la nuit. Soleil jour. Lune nuit. Plus tard, Gaëtane se réveille un peu. Elle se souvient. Le jour, le soleil. La nuit, la lune. Dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1513,7 @@
           <t>narrateur|La lune est là. Quel moment est-ce ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1685,7 @@
           <t>narrateur|Gaëtane a vu le soleil le jour. Elle a vu la lune la nuit. Elle fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1841,6 +1853,7 @@
           <t>narrateur|Maman baisse la lumière. Gaëtane respire.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2008,6 +2021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2050,6 +2064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2251,6 +2279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.JOU.001-07.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gaëtane nomme le soleil et la lune</t>
+          <t>L'étoile du grenier</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah veut compter les étoiles depuis la fenêtre du toit du grenier. Le soleil chauffe les planches. Le soir, trop de nuages. Une étoile passe quand même. Elles la gardent.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le jour, Gaëtane joue au jardin avec maman. Le soleil brille. Il fait chaud sur les mains. Le jour, c'est le soleil. Gaëtane touche une pierre tiède. Parce que le soleil a chauffé. Elles rangent le seau. Le soir arrive. Le ciel devient bleu foncé. Gaëtane voit la lune. Elle voit les étoiles. La nuit, c'est la lune. Elles rentrent. Gaëtane met son pyjama. La nuit, on fait dodo. Gaëtane se couche. Elle ferme les yeux. Dodo la nuit. Soleil jour. Lune nuit. Plus tard, Gaëtane se réveille un peu. Elle se souvient. Le jour, le soleil. La nuit, la lune. Dodo la nuit.</t>
+          <t>Un carré de ciel tient dans la fenêtre du toit. Un rayon traverse la poussière au-dessus du coffre. Les planches du grenier sentent le bois chaud. Sarah vit ici, avec maman. Un tapis râpé attend sous la fenêtre du toit. Un coussin bleu est posé dessus. Tu veux monter encore ? Oui, maman. Je veux compter les étoiles. Ce soir, si le ciel se dégage. En ce moment, Sarah s'assoit sur le coussin. Le soleil lui chauffe les genoux. Un oiseau passe dans le carré de ciel. Le jour, c'est le soleil. Il est trop fort pour les étoiles. Elles attendent la nuit. Sarah ouvre le coffre un peu. Une couverture à carreaux sent la lavande. Elles la plient près du tapis. Le rayon glisse vers le mur. La poussière danse moins. Le carré de ciel devient plus pâle. Le jour s'en va. Sarah reste sous la fenêtre du toit. Le grenier refroidit, tout doucement. Le ciel vire au bleu foncé. Les étoiles ? Des nuages gris bouchent le carré. Pas une étoile. Pas la lune non plus. Il y en a trop, des nuages. On attend un peu ? Sarah pose le menton sur le coussin. Maman s'assoit contre le coffre. Le bois craque, tout bas. Un nuage se déchire, très lentement. Une lune ronde entre dans la fenêtre du toit. La lune ! La nuit, c'est la lune. Sarah cherche les étoiles autour. Le nuage cache encore presque tout. Je n'en vois pas. Regarde le bord, tout à droite. Une étoile minuscule pique le ciel. Une ! Bravo. Tu l'as trouvée. Sarah la compte tout haut. Un. Le nuage n'en laisse pas d'autre. C'est déjà beaucoup. Oui. Une étoile, et la lune.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le jour, Gaëtane joue au jardin avec maman. Le &lt;emphasis level="moderate"&gt;soleil&lt;/emphasis&gt; brille. Il fait chaud sur les mains. Maman dit : le jour, c'est le soleil. Gaëtane touche une pierre tiède. Parce que le soleil a chauffé. Elles rangent le seau. Le soir arrive. Le ciel devient bleu foncé. Gaëtane voit la lune. Elle voit les étoiles. Maman dit : la nuit, c'est la lune. Elles rentrent. Gaëtane met son pyjama. Maman dit : la nuit, on fait dodo. Gaëtane se couche. Elle ferme les yeux. Dodo la nuit. Soleil jour. Lune nuit. Plus tard, Gaëtane se réveille un peu. Elle se souvient. Le jour, le soleil. La nuit, la lune. Dodo la nuit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un carré de ciel tient dans la fenêtre du toit. Un rayon traverse la poussière au-dessus du coffre. Les planches du grenier sentent le bois chaud. Sarah vit ici, avec maman. Un tapis râpé attend sous la fenêtre du toit. Un coussin bleu est posé dessus. Tu veux monter encore ? Oui, maman. Je veux compter les étoiles. Ce soir, si le ciel se dégage. En ce moment, Sarah s'assoit sur le coussin. Le soleil lui chauffe les genoux. Un oiseau passe dans le carré de ciel. Le jour, c'est le soleil. Il est trop fort pour les étoiles. Elles attendent la nuit. Sarah ouvre le coffre un peu. Une couverture à carreaux sent la lavande. Elles la plient près du tapis. Le rayon glisse vers le mur. La poussière danse moins. Le carré de ciel devient plus pâle. Le jour s'en va. Sarah reste sous la fenêtre du toit. Le grenier refroidit, tout doucement. Le ciel vire au bleu foncé. Les étoiles ? Des nuages gris bouchent le carré. Pas une étoile. Pas la lune non plus. Il y en a trop, des nuages. On attend un peu ? Sarah pose le menton sur le coussin. Maman s'assoit contre le coffre. Le bois craque, tout bas. Un nuage se déchire, très lentement. Une lune ronde entre dans la fenêtre du toit. La lune ! La nuit, c'est la lune. Sarah cherche les étoiles autour. Le nuage cache encore presque tout. Je n'en vois pas. Regarde le bord, tout à droite. Une étoile minuscule pique le ciel. Une ! Bravo. Tu l'as trouvée. Sarah la compte tout haut. Un. Le nuage n'en laisse pas d'autre. C'est déjà beaucoup. Oui. Une étoile, et la lune.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,59 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le jour, Gaëtane joue au jardin avec maman. Le soleil brille. Il fait chaud sur les mains.
+          <t>narrateur|Un carré de ciel tient dans la fenêtre du toit.
+narrateur|Un rayon traverse la poussière au-dessus du coffre.
+narrateur|Les planches du grenier sentent le bois chaud.
+narrateur|Sarah vit ici, avec maman.
+narrateur|Un tapis râpé attend sous la fenêtre du toit.
+narrateur|Un coussin bleu est posé dessus.
+maman|Tu veux monter encore ?
+enfant-f|Oui, maman.
+enfant-f|Je veux compter les étoiles.
+maman|Ce soir, si le ciel se dégage.
+narrateur|En ce moment, Sarah s'assoit sur le coussin.
+narrateur|Le soleil lui chauffe les genoux.
+narrateur|Un oiseau passe dans le carré de ciel.
 maman|Le jour, c'est le soleil.
-narrateur|Gaëtane touche une pierre tiède. Parce que le soleil a chauffé. Elles rangent le seau. Le soir arrive. Le ciel devient bleu foncé. Gaëtane voit la lune. Elle voit les étoiles.
-maman|La nuit, c'est la lune. Elles rentrent.
-narrateur|Gaëtane met son pyjama.
-maman|La nuit, on fait dodo.
-narrateur|Gaëtane se couche. Elle ferme les yeux. Dodo la nuit. Soleil jour. Lune nuit. Plus tard, Gaëtane se réveille un peu. Elle se souvient. Le jour, le soleil. La nuit, la lune. Dodo la nuit.</t>
+enfant-f|Il est trop fort pour les étoiles.
+maman|Elles attendent la nuit.
+narrateur|Sarah ouvre le coffre un peu.
+narrateur|Une couverture à carreaux sent la lavande.
+narrateur|Elles la plient près du tapis.
+narrateur|Le rayon glisse vers le mur.
+narrateur|La poussière danse moins.
+narrateur|Le carré de ciel devient plus pâle.
+maman|Le jour s'en va.
+narrateur|Sarah reste sous la fenêtre du toit.
+narrateur|Le grenier refroidit, tout doucement.
+narrateur|Le ciel vire au bleu foncé.
+enfant-f|Les étoiles ?
+narrateur|Des nuages gris bouchent le carré.
+narrateur|Pas une étoile.
+narrateur|Pas la lune non plus.
+enfant-f|Il y en a trop, des nuages.
+maman|On attend un peu ?
+narrateur|Sarah pose le menton sur le coussin.
+narrateur|Maman s'assoit contre le coffre.
+narrateur|Le bois craque, tout bas.
+narrateur|Un nuage se déchire, très lentement.
+narrateur|Une lune ronde entre dans la fenêtre du toit.
+enfant-f|La lune !
+maman|La nuit, c'est la lune.
+narrateur|Sarah cherche les étoiles autour.
+narrateur|Le nuage cache encore presque tout.
+enfant-f|Je n'en vois pas.
+maman|Regarde le bord, tout à droite.
+narrateur|Une étoile minuscule pique le ciel.
+enfant-f|Une !
+maman|Bravo.
+maman|Tu l'as trouvée.
+narrateur|Sarah la compte tout haut.
+narrateur|Un.
+narrateur|Le nuage n'en laisse pas d'autre.
+enfant-f|C'est déjà beaucoup.
+maman|Oui.
+maman|Une étoile, et la lune.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1350,12 +1408,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La lune est là. Quel moment est-ce ?</t>
+          <t>La lune est dans la fenêtre du toit. Quel moment est-ce ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;lune&lt;/emphasis&gt; est là. Quel moment est-ce ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La lune est dans la fenêtre du toit. Quel moment est-ce ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1427,14 +1485,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1510,10 +1568,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La lune est là. Quel moment est-ce ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|La lune est dans la fenêtre du toit.
+narrateur|Quel moment est-ce ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1538,12 +1596,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gaëtane a vu le soleil le jour. Elle a vu la lune la nuit. Elle fait dodo la nuit.</t>
+          <t>Sarah garde les yeux sur le carré. C'est la nuit. Oui. Le jour, le soleil. La nuit, la lune. Elles enroulent la couverture à carreaux. Sarah a les pieds froids. On descend se coucher ? Encore une minute. L'étoile tient toujours, toute seule. La lune glisse un peu dans le bois de la fenêtre du toit. Je l'ai comptée. Un. C'était la tienne. Sarah ferme le coffre. La lavande reste dans l'air. Elles descendent l'escalier étroit. Les marches parlent sous les pieds. Dans la chambre, Sarah met son pyjama. La nuit, on fait dodo. Mon étoile aussi ? Elle veille un peu. Sarah se glisse sous le drap. Elle revoit le carré, et le un.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gaëtane a vu le &lt;emphasis level="moderate"&gt;soleil&lt;/emphasis&gt; le jour. Elle a vu la lune la nuit. Elle fait dodo la nuit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah garde les yeux sur le carré. C'est la nuit. Oui. Le jour, le soleil. La nuit, la lune. Elles enroulent la couverture à carreaux. Sarah a les pieds froids. On descend se coucher ? Encore une minute. L'étoile tient toujours, toute seule. La lune glisse un peu dans le bois de la fenêtre du toit. Je l'ai comptée. Un. C'était la tienne. Sarah ferme le coffre. La lavande reste dans l'air. Elles descendent l'escalier étroit. Les marches parlent sous les pieds. Dans la chambre, Sarah met son pyjama. La nuit, on fait dodo. Mon étoile aussi ? Elle veille un peu. Sarah se glisse sous le drap. Elle revoit le carré, et le un.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1606,7 +1664,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1682,10 +1740,32 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Gaëtane a vu le soleil le jour. Elle a vu la lune la nuit. Elle fait dodo la nuit.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah garde les yeux sur le carré.
+enfant-f|C'est la nuit.
+maman|Oui.
+maman|Le jour, le soleil.
+maman|La nuit, la lune.
+narrateur|Elles enroulent la couverture à carreaux.
+narrateur|Sarah a les pieds froids.
+maman|On descend se coucher ?
+enfant-f|Encore une minute.
+narrateur|L'étoile tient toujours, toute seule.
+narrateur|La lune glisse un peu dans le bois de la fenêtre du toit.
+enfant-f|Je l'ai comptée.
+maman|Un.
+maman|C'était la tienne.
+narrateur|Sarah ferme le coffre.
+narrateur|La lavande reste dans l'air.
+narrateur|Elles descendent l'escalier étroit.
+narrateur|Les marches parlent sous les pieds.
+narrateur|Dans la chambre, Sarah met son pyjama.
+maman|La nuit, on fait dodo.
+enfant-f|Mon étoile aussi ?
+maman|Elle veille un peu.
+narrateur|Sarah se glisse sous le drap.
+narrateur|Elle revoit le carré, et le un.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1710,12 +1790,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman baisse la lumière. Gaëtane respire.</t>
+          <t>Maman baisse la lumière. La chambre sent encore le bois du grenier. Tu la revois ? Oui. Tout à droite. Sarah respire, tout doucement. Ses genoux gardent un peu de soleil.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman bais&lt;emphasis level="moderate"&gt;se&lt;/emphasis&gt; la lumière. Gaëtane respire.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman baisse la lumière. La chambre sent encore le bois du grenier. Tu la revois ? Oui. Tout à droite. Sarah respire, tout doucement. Ses genoux gardent un peu de soleil.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1778,7 +1858,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1850,10 +1930,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman baisse la lumière. Gaëtane respire.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Maman baisse la lumière.
+narrateur|La chambre sent encore le bois du grenier.
+maman|Tu la revois ?
+enfant-f|Oui.
+enfant-f|Tout à droite.
+narrateur|Sarah respire, tout doucement.
+narrateur|Ses genoux gardent un peu de soleil.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1878,12 +1963,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Au-dessus, la fenêtre du toit tient encore le ciel. La lune y est, ronde. L'étoile minuscule pique le bord. Un. Un. Le coussin bleu attend sous le carré.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Au-dessus, la fenêtre du toit tient encore le ciel. La lune y est, ronde. L'étoile minuscule pique le bord. Un. Un. Le coussin bleu attend sous le carré.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1946,7 +2031,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2018,10 +2103,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Au-dessus, la fenêtre du toit tient encore le ciel.
+narrateur|La lune y est, ronde.
+narrateur|L'étoile minuscule pique le bord.
+enfant-f|Un.
+maman|Un.
+narrateur|Le coussin bleu attend sous le carré.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2040,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2167,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.JOU.001-07.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin puis chambre</t>
+          <t>grenier à fenêtre du toit, jour puis nuit</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gaëtane, maman</t>
+          <t>Sarah, maman</t>
         </is>
       </c>
     </row>
